--- a/verification/cases/roundtrip/themes/init.xlsx
+++ b/verification/cases/roundtrip/themes/init.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1DB0D4F0-378D-4F4D-BE09-E62B97E3AD19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="360" windowWidth="19875" windowHeight="11535"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -55,7 +61,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -162,10 +168,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -193,14 +198,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -238,7 +246,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -310,7 +318,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -483,70 +491,70 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
         <v>11</v>
       </c>
     </row>
